--- a/data/trans_dic/P56$familiarvive-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P56$familiarvive-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,49</t>
+          <t>0,0; 44,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,44</t>
+          <t>0,0; 41,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,37; 40,07</t>
+          <t>5,34; 45,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,42</t>
+          <t>0,0; 37,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 43,31</t>
+          <t>4,62; 43,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,01</t>
+          <t>0,0; 73,29</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,08; 32,08</t>
+          <t>4,11; 35,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 28,84</t>
+          <t>2,83; 27,39</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 27,84</t>
+          <t>3,06; 28,42</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,91</t>
+          <t>0,0; 72,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,86</t>
+          <t>0,0; 48,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,31; 85,59</t>
+          <t>12,91; 85,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,21; 57,05</t>
+          <t>7,2; 56,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,76; 64,05</t>
+          <t>14,29; 64,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,82; 61,9</t>
+          <t>29,56; 61,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,24; 72,63</t>
+          <t>16,02; 72,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,98; 43,08</t>
+          <t>21,11; 43,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,06; 57,6</t>
+          <t>15,39; 55,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,14; 52,38</t>
+          <t>21,64; 51,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21,27; 67,48</t>
+          <t>23,07; 71,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,8; 41,38</t>
+          <t>21,03; 41,11</t>
         </is>
       </c>
     </row>
@@ -1002,57 +1002,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,1</t>
+          <t>0,0; 49,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,39</t>
+          <t>0,0; 69,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 27,92</t>
+          <t>2,61; 24,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,22; 81,57</t>
+          <t>24,88; 82,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,68; 45,57</t>
+          <t>5,69; 45,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,8; 79,43</t>
+          <t>11,52; 86,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,8; 37,92</t>
+          <t>16,66; 38,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,94; 76,59</t>
+          <t>26,4; 77,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,47; 39,05</t>
+          <t>6,87; 36,93</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,66; 65,44</t>
+          <t>19,08; 70,38</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,35; 29,37</t>
+          <t>14,29; 29,88</t>
         </is>
       </c>
     </row>
@@ -1142,57 +1142,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,65</t>
+          <t>0,0; 54,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,74</t>
+          <t>0,0; 49,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,07</t>
+          <t>0,0; 61,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,21; 47,4</t>
+          <t>9,06; 44,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 36,55</t>
+          <t>4,5; 39,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 20,6</t>
+          <t>3,88; 22,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,03; 56,72</t>
+          <t>7,82; 58,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,75; 40,45</t>
+          <t>6,96; 37,84</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,14; 34,21</t>
+          <t>5,48; 32,83</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 15,36</t>
+          <t>2,63; 14,18</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1287,52 +1287,52 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,93</t>
+          <t>0,0; 25,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,27; 87,53</t>
+          <t>13,91; 85,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,52; 63,69</t>
+          <t>20,38; 67,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,39</t>
+          <t>0,0; 50,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,47; 28,05</t>
+          <t>6,73; 26,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,24; 66,3</t>
+          <t>9,18; 65,68</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,14; 62,8</t>
+          <t>22,67; 59,23</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,15; 56,79</t>
+          <t>6,07; 53,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,0; 22,6</t>
+          <t>6,33; 24,55</t>
         </is>
       </c>
     </row>
@@ -1422,57 +1422,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,15</t>
+          <t>0,0; 39,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,03; 51,87</t>
+          <t>6,97; 52,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,62; 23,44</t>
+          <t>2,73; 24,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,46; 80,61</t>
+          <t>13,25; 80,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,35; 37,7</t>
+          <t>5,37; 38,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,47; 53,64</t>
+          <t>10,67; 55,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,3; 20,22</t>
+          <t>5,88; 20,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21,44; 79,05</t>
+          <t>23,2; 77,75</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,52; 27,94</t>
+          <t>3,52; 28,3</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12,48; 44,64</t>
+          <t>12,7; 44,92</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,07; 18,12</t>
+          <t>6,84; 17,88</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,84</t>
+          <t>0,0; 69,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,88; 59,21</t>
+          <t>6,42; 60,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,22</t>
+          <t>0,0; 26,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,77</t>
+          <t>0,0; 34,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,37 +1582,37 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,94; 44,05</t>
+          <t>11,52; 44,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,14; 45,09</t>
+          <t>13,68; 44,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,4; 29,86</t>
+          <t>11,29; 30,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,09; 68,59</t>
+          <t>9,75; 64,15</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15,18; 43,27</t>
+          <t>14,09; 41,79</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10,37; 32,35</t>
+          <t>10,67; 32,42</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,69; 27,71</t>
+          <t>10,72; 26,7</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,6</t>
+          <t>0,0; 32,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,44; 87,02</t>
+          <t>13,45; 88,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,1</t>
+          <t>0,0; 39,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,75; 37,89</t>
+          <t>8,68; 36,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,04; 56,73</t>
+          <t>19,58; 58,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,54; 43,31</t>
+          <t>10,74; 45,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,11; 58,15</t>
+          <t>11,84; 55,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,75; 33,86</t>
+          <t>17,7; 34,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,26; 41,53</t>
+          <t>14,48; 41,26</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16,8; 48,96</t>
+          <t>16,75; 48,79</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,17; 43,6</t>
+          <t>11,46; 45,57</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,48; 31,01</t>
+          <t>16,87; 31,54</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,93; 31,83</t>
+          <t>9,98; 31,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12,0; 32,85</t>
+          <t>11,3; 32,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10,08; 27,03</t>
+          <t>9,8; 25,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,79; 19,05</t>
+          <t>8,69; 19,7</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30,8; 51,58</t>
+          <t>30,49; 51,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,88; 34,68</t>
+          <t>22,53; 35,76</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,26; 34,14</t>
+          <t>19,54; 34,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18,19; 25,71</t>
+          <t>18,03; 25,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25,87; 41,88</t>
+          <t>26,57; 41,94</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20,36; 31,59</t>
+          <t>20,46; 31,17</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18,0; 29,82</t>
+          <t>18,4; 29,99</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16,2; 22,32</t>
+          <t>16,43; 22,21</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,22 +2209,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1276</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4124</t>
+          <t>0; 3119</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4115</t>
+          <t>0; 4078</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1169</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2234,37 +2234,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1141; 8508</t>
+          <t>1135; 9744</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6881</t>
+          <t>0; 6888</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>365; 3563</t>
+          <t>380; 3612</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4381</t>
+          <t>0; 4339</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1153; 9075</t>
+          <t>1164; 10025</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>787; 8167</t>
+          <t>800; 7757</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>383; 3691</t>
+          <t>406; 3768</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4948</t>
+          <t>0; 5004</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4668</t>
+          <t>0; 5663</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>675; 4695</t>
+          <t>708; 4715</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>879; 6960</t>
+          <t>879; 6952</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2024; 9421</t>
+          <t>2102; 9516</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10637; 22848</t>
+          <t>10909; 22840</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2894; 12941</t>
+          <t>2855; 12890</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8794; 18060</t>
+          <t>8850; 18060</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3250; 12434</t>
+          <t>3322; 11952</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10765; 25465</t>
+          <t>10521; 25274</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4957; 15724</t>
+          <t>5376; 16582</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11257; 22394</t>
+          <t>11384; 22250</t>
         </is>
       </c>
     </row>
@@ -2630,57 +2630,57 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4550</t>
+          <t>0; 4557</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4291</t>
+          <t>0; 4171</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>482; 5113</t>
+          <t>479; 4494</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2723; 9996</t>
+          <t>3049; 10124</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1094; 8776</t>
+          <t>1096; 8779</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1163; 8557</t>
+          <t>1241; 9342</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5296; 12707</t>
+          <t>5582; 12768</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3484; 11631</t>
+          <t>4010; 11777</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2132; 11138</t>
+          <t>1961; 10533</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2797; 10983</t>
+          <t>3203; 11813</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6918; 15222</t>
+          <t>7406; 15487</t>
         </is>
       </c>
     </row>
@@ -2838,57 +2838,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5267</t>
+          <t>0; 4770</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4977</t>
+          <t>0; 4904</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 1097</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5631</t>
+          <t>0; 6639</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2068; 10644</t>
+          <t>2034; 9980</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1155; 9110</t>
+          <t>1121; 9859</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>763; 4074</t>
+          <t>768; 4454</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1075; 7598</t>
+          <t>1047; 7787</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3037; 12597</t>
+          <t>2168; 11784</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2143; 11950</t>
+          <t>1914; 11469</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>776; 4460</t>
+          <t>765; 4119</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1309</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3051,52 +3051,52 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>183; 799</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2320</t>
+          <t>0; 1903</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1186; 7821</t>
+          <t>1243; 7684</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4042; 12547</t>
+          <t>4015; 13266</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6589</t>
+          <t>0; 6108</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1073; 4652</t>
+          <t>1116; 4446</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1221; 8763</t>
+          <t>1213; 8681</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6111; 16584</t>
+          <t>5986; 15639</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>794; 7334</t>
+          <t>784; 6870</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1446; 5443</t>
+          <t>1525; 5913</t>
         </is>
       </c>
     </row>
@@ -3254,57 +3254,57 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4169</t>
+          <t>0; 4163</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>760; 5608</t>
+          <t>753; 5695</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>432; 3873</t>
+          <t>451; 3998</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1314; 8503</t>
+          <t>1398; 8440</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1079; 7613</t>
+          <t>1085; 7708</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2315; 11857</t>
+          <t>2359; 12278</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2002; 6423</t>
+          <t>1869; 6526</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3053; 11253</t>
+          <t>3303; 11068</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1085; 8618</t>
+          <t>1087; 8728</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4107; 14695</t>
+          <t>4181; 14787</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3412; 8752</t>
+          <t>3303; 8633</t>
         </is>
       </c>
     </row>
@@ -3457,22 +3457,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3519</t>
+          <t>0; 3603</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>914; 9208</t>
+          <t>999; 9480</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 5430</t>
+          <t>0; 5232</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4066</t>
+          <t>0; 4321</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3482,37 +3482,37 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4229; 15607</t>
+          <t>4081; 15870</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6065; 19346</t>
+          <t>5869; 18906</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4781; 12518</t>
+          <t>4732; 12793</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>922; 6269</t>
+          <t>891; 5863</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7741; 22061</t>
+          <t>7183; 21303</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6520; 20334</t>
+          <t>6703; 20377</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5808; 15055</t>
+          <t>5824; 14509</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 5879</t>
+          <t>0; 6180</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1194; 7732</t>
+          <t>1195; 7887</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 4106</t>
+          <t>0; 3629</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1820; 7881</t>
+          <t>1805; 7581</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>5998; 16979</t>
+          <t>5862; 17499</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3169; 13019</t>
+          <t>3228; 13764</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3439; 13234</t>
+          <t>2694; 12685</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>9605; 19415</t>
+          <t>10147; 19644</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>7502; 20410</t>
+          <t>7115; 20279</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6542; 19070</t>
+          <t>6524; 19004</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3239; 13893</t>
+          <t>3652; 14522</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>13660; 24232</t>
+          <t>13184; 24646</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>4792; 15366</t>
+          <t>4817; 15129</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9419; 25791</t>
+          <t>8874; 25277</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7267; 19490</t>
+          <t>7062; 18504</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8975; 19445</t>
+          <t>8866; 20107</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>28816; 48252</t>
+          <t>28525; 48161</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>44914; 71179</t>
+          <t>46249; 73395</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33081; 58651</t>
+          <t>33564; 59659</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>45665; 64538</t>
+          <t>45255; 64689</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>36686; 59390</t>
+          <t>37688; 59486</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>57759; 89642</t>
+          <t>58046; 88452</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>43897; 72721</t>
+          <t>44872; 73135</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>57186; 78795</t>
+          <t>57999; 78421</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$familiarvive-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P56$familiarvive-Provincia-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,23</t>
+          <t>0,0; 58,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,06</t>
+          <t>0,0; 33,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,34; 45,88</t>
+          <t>5,37; 42,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,46</t>
+          <t>0,0; 35,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 43,91</t>
+          <t>5,59; 42,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,29</t>
+          <t>0,0; 69,55</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,11; 35,44</t>
+          <t>4,07; 34,96</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 27,39</t>
+          <t>2,63; 26,66</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,06; 28,42</t>
+          <t>3,34; 30,58</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,58%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,74</t>
+          <t>0,0; 72,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,36</t>
+          <t>0,0; 44,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,91; 85,97</t>
+          <t>13,71; 85,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,2; 56,98</t>
+          <t>7,09; 57,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,29; 64,7</t>
+          <t>13,9; 62,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,56; 61,88</t>
+          <t>28,39; 63,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,02; 72,34</t>
+          <t>16,04; 72,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,11; 43,08</t>
+          <t>20,63; 44,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,39; 55,36</t>
+          <t>15,29; 58,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,64; 51,98</t>
+          <t>22,25; 50,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23,07; 71,16</t>
+          <t>24,37; 69,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,03; 41,11</t>
+          <t>20,25; 41,09</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -1002,57 +1002,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,17</t>
+          <t>0,0; 49,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,39</t>
+          <t>0,0; 66,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 24,54</t>
+          <t>2,77; 27,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,88; 82,62</t>
+          <t>26,23; 81,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,69; 45,59</t>
+          <t>5,68; 45,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,52; 86,71</t>
+          <t>11,59; 86,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,66; 38,1</t>
+          <t>16,88; 37,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,4; 77,54</t>
+          <t>26,5; 77,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,87; 36,93</t>
+          <t>6,93; 38,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19,08; 70,38</t>
+          <t>13,92; 65,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,29; 29,88</t>
+          <t>13,74; 29,11</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,92</t>
+          <t>0,0; 49,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,01</t>
+          <t>0,0; 49,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1157,42 +1157,42 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,39</t>
+          <t>0,0; 51,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,06; 44,45</t>
+          <t>9,14; 47,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,5; 39,56</t>
+          <t>0,0; 36,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 22,53</t>
+          <t>3,79; 21,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,82; 58,14</t>
+          <t>7,88; 59,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,96; 37,84</t>
+          <t>7,52; 37,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,48; 32,83</t>
+          <t>6,47; 35,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,63; 14,18</t>
+          <t>1,54; 14,32</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,79</t>
+          <t>0,0; 82,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,47 +1292,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,37</t>
+          <t>0,0; 26,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,91; 85,99</t>
+          <t>13,34; 87,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,38; 67,34</t>
+          <t>20,38; 64,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,42</t>
+          <t>0,0; 48,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,73; 26,81</t>
+          <t>6,54; 28,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,18; 65,68</t>
+          <t>9,23; 66,53</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22,67; 59,23</t>
+          <t>19,87; 59,61</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,07; 53,2</t>
+          <t>6,07; 55,88</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,33; 24,55</t>
+          <t>5,9; 23,32</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1422,57 +1422,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,09</t>
+          <t>0,0; 39,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,97; 52,67</t>
+          <t>7,14; 52,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,73; 24,19</t>
+          <t>2,54; 23,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,25; 80,01</t>
+          <t>13,63; 81,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,37; 38,17</t>
+          <t>5,34; 37,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,67; 55,55</t>
+          <t>11,05; 54,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,88; 20,55</t>
+          <t>6,61; 20,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23,2; 77,75</t>
+          <t>18,83; 78,06</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,52; 28,3</t>
+          <t>3,53; 30,84</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12,7; 44,92</t>
+          <t>11,84; 46,71</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,84; 17,88</t>
+          <t>7,11; 18,33</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -1562,17 +1562,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,42; 60,96</t>
+          <t>6,29; 60,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,23</t>
+          <t>0,0; 24,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,82</t>
+          <t>0,0; 37,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,37 +1582,37 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,52; 44,79</t>
+          <t>11,56; 44,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,68; 44,07</t>
+          <t>14,15; 45,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,29; 30,51</t>
+          <t>11,57; 29,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,75; 64,15</t>
+          <t>10,05; 64,9</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14,09; 41,79</t>
+          <t>13,78; 41,7</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10,67; 32,42</t>
+          <t>10,47; 32,27</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,72; 26,7</t>
+          <t>10,67; 27,5</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,17</t>
+          <t>0,0; 33,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,45; 88,76</t>
+          <t>13,35; 88,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,87</t>
+          <t>0,0; 40,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,68; 36,44</t>
+          <t>8,45; 35,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,58; 58,46</t>
+          <t>18,79; 58,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,74; 45,78</t>
+          <t>13,62; 43,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,84; 55,74</t>
+          <t>14,36; 54,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17,7; 34,26</t>
+          <t>17,43; 33,31</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,48; 41,26</t>
+          <t>13,93; 40,42</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16,75; 48,79</t>
+          <t>16,84; 49,05</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11,46; 45,57</t>
+          <t>11,44; 43,24</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,87; 31,54</t>
+          <t>16,56; 31,05</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,98; 31,33</t>
+          <t>9,48; 31,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,3; 32,2</t>
+          <t>10,89; 31,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,8; 25,67</t>
+          <t>9,32; 25,96</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,69; 19,7</t>
+          <t>8,63; 19,97</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30,49; 51,48</t>
+          <t>30,27; 51,76</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,53; 35,76</t>
+          <t>22,16; 35,12</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,54; 34,73</t>
+          <t>19,62; 34,6</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18,03; 25,77</t>
+          <t>17,97; 25,74</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>26,57; 41,94</t>
+          <t>26,23; 41,11</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20,46; 31,17</t>
+          <t>19,94; 31,68</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18,4; 29,99</t>
+          <t>18,57; 29,98</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16,43; 22,21</t>
+          <t>16,14; 22,32</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1500</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3119</t>
+          <t>0; 4115</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4078</t>
+          <t>0; 3361</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2234,37 +2234,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1135; 9744</t>
+          <t>1140; 8930</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6888</t>
+          <t>0; 6575</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>380; 3612</t>
+          <t>472; 3559</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4339</t>
+          <t>0; 4117</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1164; 10025</t>
+          <t>1151; 9888</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>800; 7757</t>
+          <t>746; 7549</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>406; 3768</t>
+          <t>459; 4195</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3699</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13090</t>
+          <t>13972</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16583</t>
+          <t>17672</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5004</t>
+          <t>0; 4988</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5663</t>
+          <t>0; 5225</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>708; 4715</t>
+          <t>752; 4692</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>879; 6952</t>
+          <t>928; 7488</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2102; 9516</t>
+          <t>2045; 9222</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10909; 22840</t>
+          <t>10477; 23618</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2855; 12890</t>
+          <t>2857; 12834</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8850; 18060</t>
+          <t>9225; 19683</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3322; 11952</t>
+          <t>3300; 12655</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10521; 25274</t>
+          <t>10819; 24760</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5376; 16582</t>
+          <t>5679; 16179</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11384; 22250</t>
+          <t>11702; 23750</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1754</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8743</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10522</t>
+          <t>10620</t>
         </is>
       </c>
     </row>
@@ -2630,57 +2630,57 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4557</t>
+          <t>0; 4596</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4171</t>
+          <t>0; 4027</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>479; 4494</t>
+          <t>495; 4828</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3049; 10124</t>
+          <t>3214; 9986</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1096; 8779</t>
+          <t>1094; 8696</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1241; 9342</t>
+          <t>1248; 9337</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5582; 12768</t>
+          <t>5664; 12668</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4010; 11777</t>
+          <t>4025; 11792</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1961; 10533</t>
+          <t>1977; 10956</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3203; 11813</t>
+          <t>2336; 10971</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7406; 15487</t>
+          <t>7064; 14970</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2110</t>
         </is>
       </c>
     </row>
@@ -2838,12 +2838,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4770</t>
+          <t>0; 4298</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4904</t>
+          <t>0; 4929</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2853,42 +2853,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6639</t>
+          <t>0; 5609</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2034; 9980</t>
+          <t>2052; 10667</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1121; 9859</t>
+          <t>0; 9121</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>768; 4454</t>
+          <t>789; 4579</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1047; 7787</t>
+          <t>1055; 7925</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2168; 11784</t>
+          <t>2341; 11694</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1914; 11469</t>
+          <t>2260; 12537</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>765; 4119</t>
+          <t>467; 4344</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>483</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2573</t>
+          <t>2675</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3158</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5552</t>
+          <t>0; 5548</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3056,47 +3056,47 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1903</t>
+          <t>0; 2067</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1243; 7684</t>
+          <t>1192; 7833</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4015; 13266</t>
+          <t>4015; 12624</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6108</t>
+          <t>0; 5836</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1116; 4446</t>
+          <t>1127; 4917</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1213; 8681</t>
+          <t>1220; 8793</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5986; 15639</t>
+          <t>5246; 15741</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>784; 6870</t>
+          <t>784; 7216</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1525; 5913</t>
+          <t>1468; 5805</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5590</t>
+          <t>5685</t>
         </is>
       </c>
     </row>
@@ -3254,57 +3254,57 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4163</t>
+          <t>0; 4170</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>753; 5695</t>
+          <t>773; 5680</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>451; 3998</t>
+          <t>421; 3898</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1398; 8440</t>
+          <t>1438; 8575</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1085; 7708</t>
+          <t>1079; 7603</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2359; 12278</t>
+          <t>2443; 12080</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1869; 6526</t>
+          <t>2151; 6718</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3303; 11068</t>
+          <t>2680; 11112</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1087; 8728</t>
+          <t>1088; 9514</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4181; 14787</t>
+          <t>3897; 15377</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3303; 8633</t>
+          <t>3492; 9001</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>9980</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>9716</t>
+          <t>11817</t>
         </is>
       </c>
     </row>
@@ -3462,17 +3462,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>999; 9480</t>
+          <t>978; 9361</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 5232</t>
+          <t>0; 4906</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4321</t>
+          <t>0; 5572</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3482,37 +3482,37 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4081; 15870</t>
+          <t>4097; 15759</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5869; 18906</t>
+          <t>6070; 19494</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4732; 12793</t>
+          <t>5973; 15327</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>891; 5863</t>
+          <t>918; 5932</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7183; 21303</t>
+          <t>7025; 21260</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6703; 20377</t>
+          <t>6583; 20282</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5824; 14509</t>
+          <t>7100; 18300</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>4739</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>14334</t>
+          <t>16316</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>18612</t>
+          <t>21055</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 6180</t>
+          <t>0; 6504</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1195; 7887</t>
+          <t>1186; 7858</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 3629</t>
+          <t>0; 3679</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1805; 7581</t>
+          <t>2003; 8326</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>5862; 17499</t>
+          <t>5623; 17597</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3228; 13764</t>
+          <t>4094; 13206</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2694; 12685</t>
+          <t>3269; 12513</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>10147; 19644</t>
+          <t>11589; 22147</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>7115; 20279</t>
+          <t>6844; 19862</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6524; 19004</t>
+          <t>6558; 19106</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3652; 14522</t>
+          <t>3647; 13779</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>13184; 24646</t>
+          <t>14934; 28006</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13269</t>
+          <t>14260</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>54228</t>
+          <t>59356</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>67497</t>
+          <t>73617</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>4817; 15129</t>
+          <t>4577; 15035</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>8874; 25277</t>
+          <t>8549; 24337</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7062; 18504</t>
+          <t>6720; 18714</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8866; 20107</t>
+          <t>9375; 21685</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>28525; 48161</t>
+          <t>28318; 48416</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>46249; 73395</t>
+          <t>45488; 72089</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33564; 59659</t>
+          <t>33698; 59433</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>45255; 64689</t>
+          <t>49485; 70898</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>37688; 59486</t>
+          <t>37203; 58298</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>58046; 88452</t>
+          <t>56592; 89886</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>44872; 73135</t>
+          <t>45284; 73120</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>57999; 78421</t>
+          <t>61989; 85717</t>
         </is>
       </c>
     </row>
